--- a/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,76</t>
+          <t>-1,07; 1,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,77</t>
+          <t>-2,55; 2,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,39</t>
+          <t>-0,54; 2,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,79</t>
+          <t>-1,2; 1,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,18</t>
+          <t>-0,3; 1,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,1</t>
+          <t>-2,28; 0,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,65</t>
+          <t>-2,02; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,1</t>
+          <t>-1,25; 4,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,94</t>
+          <t>-1,54; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,41</t>
+          <t>-1,61; 1,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 870,03</t>
+          <t>-58,1; 781,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 698,29</t>
+          <t>-76,08; 667,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,43</t>
+          <t>-3,01; 1,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,28</t>
+          <t>-2,49; 4,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,43</t>
+          <t>-3,94; 0,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,58</t>
+          <t>-0,54; 4,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,96; 153,03</t>
+          <t>-84,62; 163,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 277,19</t>
+          <t>-62,08; 260,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 621,94</t>
+          <t>-43,13; 539,57</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,11</t>
+          <t>-0,83; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,66</t>
+          <t>-0,87; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,63</t>
+          <t>-0,44; 1,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 160,18</t>
+          <t>-52,87; 153,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 152,11</t>
+          <t>-39,04; 140,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 155,35</t>
+          <t>-65,23; 153,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 272,34</t>
+          <t>-36,87; 277,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,79</t>
+          <t>-1,11; 1,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,18</t>
+          <t>-2,56; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,35</t>
+          <t>-0,48; 2,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,06</t>
+          <t>-1,22; 0,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,91</t>
+          <t>-0,29; 2,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,1</t>
+          <t>-2,46; 0,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,74</t>
+          <t>-2,42; 2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,72</t>
+          <t>-1,24; 4,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,86</t>
+          <t>-1,81; 2,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,1</t>
+          <t>-1,59; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 781,07</t>
+          <t>-57,1; 662,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,08; 667,89</t>
+          <t>-76,46; 649,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,62</t>
+          <t>-3,27; 1,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,52</t>
+          <t>-2,86; 4,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,33</t>
+          <t>-3,73; 0,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,17</t>
+          <t>-0,48; 4,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 163,54</t>
+          <t>-85,25; 177,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 260,75</t>
+          <t>-62,55; 261,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 227,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 539,57</t>
+          <t>-27,72; 709,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,12</t>
+          <t>-0,91; 1,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,59</t>
+          <t>-0,84; 1,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,84</t>
+          <t>-0,86; 0,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,63</t>
+          <t>-0,49; 1,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 153,6</t>
+          <t>-51,47; 155,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 140,6</t>
+          <t>-38,12; 140,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 153,28</t>
+          <t>-62,57; 157,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 277,45</t>
+          <t>-42,76; 295,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,75</t>
+          <t>-1,07; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,74</t>
+          <t>-2,67; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-85,68%</t>
+          <t>-52,21%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,32</t>
+          <t>-0,63; 2,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,83</t>
+          <t>-1,42; 0,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,18</t>
+          <t>-0,3; 2,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,1</t>
+          <t>-1,83; 0,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-36,42%</t>
+          <t>-47,7%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,67</t>
+          <t>-2,45; 2,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,52</t>
+          <t>-1,28; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,96</t>
+          <t>-1,54; 2,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,98</t>
+          <t>-1,77; 0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 662,11</t>
+          <t>-53,27; 870,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,46; 649,43</t>
+          <t>-76,37; 698,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>107,32%</t>
+          <t>135,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,38</t>
+          <t>-2,9; 1,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,08</t>
+          <t>-2,4; 4,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,67</t>
+          <t>-4,09; 0,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,14</t>
+          <t>-0,39; 4,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,25; 177,61</t>
+          <t>-84,96; 153,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 261,94</t>
+          <t>-59,22; 277,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 709,63</t>
+          <t>-29,31; 743,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,06</t>
+          <t>-0,92; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,51</t>
+          <t>-0,87; 1,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,85</t>
+          <t>-0,95; 0,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,62</t>
+          <t>-0,41; 1,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 155,31</t>
+          <t>-55,44; 160,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 140,67</t>
+          <t>-41,17; 152,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 157,67</t>
+          <t>-64,61; 155,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 295,71</t>
+          <t>-37,23; 326,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuya percepción de los madres/padres es que su peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,155 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-27,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.04570336549013657</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4200271502689474</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.08596860551213192</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2768290724284366</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,07; 1,76</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,67; 1,77</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.072206641802336</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.671694386902481</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.76314336870905</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.768337925479194</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>122,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-40,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>212,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-52,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 2,39</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 0,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,3; 2,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,83; 0,67</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.6638142262292663</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.2410442004089552</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6323220817057218</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3696640650469866</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.223473643980824</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4022713280032585</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2.126976728975122</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.5221305828917294</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-47,7%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6266730394000124</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.421537789599978</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.2988418540542673</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.830609793508848</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 2,65</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 5,1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,54; 2,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 0,85</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-53,27; 870,03</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-76,37; 698,29</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.389321269743535</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7885945350570405</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.177196127969886</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.667248038454713</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +775,285 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-27,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-63,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135,56%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.1050086453436587</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.445866310163828</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5015472810316504</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.3718589809338769</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0703562802323935</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.8014196393392976</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.3257401761049017</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.4770484603320844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 1,43</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 4,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 0,43</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,39; 4,89</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-84,96; 153,03</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-59,22; 277,19</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-29,31; 743,77</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.448333981164914</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.277262311660301</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.543275926597429</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.773077709354148</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.532737679976661</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7636721502226129</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.654177694230993</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.099428605454472</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.938699673927193</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8450251434562347</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>8.700305008822388</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>6.982861781596205</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.6261790540144683</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7075711639766419</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.347086250096355</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.036730920337749</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2723022786882752</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2229622067514584</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.6350699855449575</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.355619761628938</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.904256778239258</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.39914633141227</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.090034850913272</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.3925758755925174</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8495519078171809</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.592217594510557</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="n">
+        <v>-0.2931265794613988</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.431053774832161</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.28371061822821</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4291384625600246</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.891093117644105</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.530257604981159</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.771909997717453</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>7.437673088065475</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 1,11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 1,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 0,84</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,41; 1,94</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-55,44; 160,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-41,17; 152,11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-64,61; 155,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-37,23; 326,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.08599270389807334</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3627752514637639</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.008143490196063467</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6263282298702506</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.06984627803018789</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2189959501464229</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.008158841536641696</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.6209545483134117</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.9180225019575385</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.8682218429876727</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.9535373450124738</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.4067740121605278</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5543537350084948</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4116848768394563</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6460666327854516</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3722730916394555</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.111005234011843</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.660768210013083</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8362450533843127</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.938747403458357</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.60180141758428</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.52113485626649</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.553455108856382</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.266120918835711</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1061,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
